--- a/auditor-aritmetika/fixtures/modelo_demo_con_hallazgos.xlsx
+++ b/auditor-aritmetika/fixtures/modelo_demo_con_hallazgos.xlsx
@@ -765,7 +765,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D18"/>
   <sheetData>
     <row r="2">
       <c r="C2" t="str">
@@ -838,9 +838,44 @@
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>Residual repartible</v>
+      </c>
+      <c r="D14">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>Carry LP</v>
+      </c>
+      <c r="D15">
+        <f>-D14*0.75</f>
+        <v>-750000000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>Carry GP</v>
+      </c>
+      <c r="D16">
+        <f>-D14*0.25</f>
+        <v>-250000000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>Valor presente sentencia</v>
+      </c>
+      <c r="D18">
+        <f>D14/(1+((1+0.15)^(1/12)-1))^12</f>
+        <v>869565217</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
   </ignoredErrors>
 </worksheet>
 </file>
